--- a/data/trans_dic/RUIDO_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,51; 78,98</t>
+          <t>69,22; 79,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74,99; 81,71</t>
+          <t>74,92; 81,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,04; 79,29</t>
+          <t>73,32; 79,38</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>67,93; 77,82</t>
+          <t>68,35; 77,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,34; 80,47</t>
+          <t>73,65; 80,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,33; 78,15</t>
+          <t>72,18; 77,92</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67,94; 79,59</t>
+          <t>68,36; 79,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,35; 92,8</t>
+          <t>61,39; 92,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,73; 89,26</t>
+          <t>67,13; 88,7</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,83; 82,81</t>
+          <t>74,87; 83,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79,46; 85,28</t>
+          <t>79,19; 85,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,38; 83,03</t>
+          <t>78,51; 83,16</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,01; 77,81</t>
+          <t>72,76; 78,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>75,22; 85,5</t>
+          <t>75,24; 85,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,22; 81,68</t>
+          <t>75,01; 81,51</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>238387; 274837</t>
+          <t>240882; 276430</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>266049; 289868</t>
+          <t>265785; 289707</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513312; 557205</t>
+          <t>515266; 557846</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>339945; 389436</t>
+          <t>342050; 388859</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>351231; 385386</t>
+          <t>352717; 386140</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>708397; 765394</t>
+          <t>706885; 763070</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>225188; 263784</t>
+          <t>226590; 263843</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>334055; 505347</t>
+          <t>334280; 505638</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>584534; 781890</t>
+          <t>588003; 777026</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>355575; 393527</t>
+          <t>355807; 394792</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>420785; 451618</t>
+          <t>419371; 450684</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>787554; 834280</t>
+          <t>788881; 835607</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1208325; 1287758</t>
+          <t>1204150; 1291266</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1434953; 1631081</t>
+          <t>1435429; 1623612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2679933; 2910240</t>
+          <t>2672528; 2904034</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/RUIDO_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,65%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,22; 79,44</t>
+          <t>69,14; 79,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74,92; 81,66</t>
+          <t>74,84; 81,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,32; 79,38</t>
+          <t>73,49; 79,25</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>68,35; 77,71</t>
+          <t>69,31; 78,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,65; 80,63</t>
+          <t>74,49; 81,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,18; 77,92</t>
+          <t>73,28; 78,75</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>72,94%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68,36; 79,6</t>
+          <t>67,03; 78,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,39; 92,86</t>
+          <t>68,44; 77,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,13; 88,7</t>
+          <t>69,59; 76,57</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,41%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,87; 83,08</t>
+          <t>76,58; 84,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79,19; 85,11</t>
+          <t>79,62; 84,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,51; 83,16</t>
+          <t>79,2; 83,46</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,17%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,76; 78,02</t>
+          <t>73,32; 78,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>75,24; 85,1</t>
+          <t>76,73; 80,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,01; 81,51</t>
+          <t>75,81; 78,55</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>259609</t>
+          <t>282977</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>278025</t>
+          <t>298623</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>537635</t>
+          <t>581600</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>240882; 276430</t>
+          <t>260949; 299898</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>265785; 289707</t>
+          <t>285448; 311038</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>515266; 557846</t>
+          <t>557677; 601335</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>367158</t>
+          <t>398576</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>370976</t>
+          <t>414116</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>738135</t>
+          <t>812692</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>342050; 388859</t>
+          <t>372176; 418935</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>352717; 386140</t>
+          <t>395026; 430825</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>706885; 763070</t>
+          <t>782137; 840532</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>246001</t>
+          <t>272869</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>429138</t>
+          <t>266241</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>675139</t>
+          <t>539110</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>226590; 263843</t>
+          <t>250843; 291913</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>334280; 505638</t>
+          <t>249717; 281762</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>588003; 777026</t>
+          <t>514341; 565917</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>377301</t>
+          <t>410950</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>436440</t>
+          <t>478282</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>813742</t>
+          <t>889232</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>355807; 394792</t>
+          <t>392397; 430566</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>419371; 450684</t>
+          <t>461708; 492459</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>788881; 835607</t>
+          <t>865174; 911658</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1250069</t>
+          <t>1365372</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1514580</t>
+          <t>1457263</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2764650</t>
+          <t>2822634</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1204150; 1291266</t>
+          <t>1320587; 1407764</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1435429; 1623612</t>
+          <t>1424488; 1486307</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2672528; 2904034</t>
+          <t>2772875; 2873058</t>
         </is>
       </c>
     </row>
